--- a/partner_results/Arlanxeo/ClassMissingGermanDefinition_Arlanxeo.xlsx
+++ b/partner_results/Arlanxeo/ClassMissingGermanDefinition_Arlanxeo.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elongation [Arlanxeo]</t>
+          <t>elastic modulus [Arlanxeo]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +457,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid deformed axially.</t>
+          <t>The component of modulus that is related to energy storage in deformation.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vulcanization [Arlanxeo]</t>
+          <t>moving die rheometer [Arlanxeo]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The process of converting a polymer compound into an elastic network using vulcanization chemicals (e.g. sulfur) and heat (to start the reaction).</t>
+          <t>Generic name for an instrument that applies oscillatory shearing deformation at the vulcanization temperature of a compound at a given time window, using a constant frequency and amplitude.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>butadiene rubber [Arlanxeo]</t>
+          <t>E dash 23 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rubber polymer with butadiene as its only monomer.</t>
+          <t>Elastic modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,18 +503,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F Median [Arlanxeo]</t>
+          <t>vinyl content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Median value of tensile strength at break from stress-strain (tensile) measurement</t>
+          <t>Vinyl content is a quality that is based on the vinyl content in polyethylene resins that are determined by the catalyst used for manufacturing the resin.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -522,7 +526,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>loss factor at 7 percent [Arlanxeo]</t>
+          <t>mass pressure 2 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -533,7 +537,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Loss factor measured at 7% deformation (strain) measured in an amplitude sweep test</t>
+          <t>Pressure at die exit in an extruder, second measurement</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -541,22 +545,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mooney viscosity [Arlanxeo]</t>
+          <t>solution SBR [Arlanxeo]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>plan specification</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mooney Viscosity is a quality of raw and vulcanised polymersbased on the measurement of the torque necessary to rotate a disc in a cylindrical chamber filled with the rubber compound to be vulcanized and is reported in arbitrary Mooney units. It is the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
+          <t>Polymerization is performed in a solution where polymer molecules are dissolved in a solvent (e.g. hexane).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -564,7 +564,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E double dash 60 degree celcius [Arlanxeo]</t>
+          <t>trans content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -572,10 +572,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Loss modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Trans content is a quality which measures the content of trans isomer in polymers that affect melting points and solubility in polymers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -583,7 +587,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rebound mean value [Arlanxeo]</t>
+          <t>E dash 0 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -591,14 +595,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius and T = 60 degree celcius for tire compounds.</t>
+          <t>Elastic modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -606,18 +606,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>moving die rheometer [Arlanxeo]</t>
+          <t>elastic modulus G dash zero point five percent measurement1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Generic name for an instrument that applies oscillatory shearing deformation at the vulcanization temperature of a compound at a given time window, using a constant frequency and amplitude.</t>
+          <t>Elastic modulus at 0.5% deformation (strain) in amplitude sweep test</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -625,18 +625,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>raw polymer [Arlanxeo]</t>
+          <t>E double dash 0 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>polymer</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Polymer (e.g. BR, SSBR) before being compounded.</t>
+          <t>Loss modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -644,18 +644,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>elastic modulus [Arlanxeo]</t>
+          <t>carbon black [Arlanxeo]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>filler [Arlanxeo]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The component of modulus that is related to energy storage in deformation.</t>
+          <t>A filler based on structured carbon which is present in larger fractions in sidewall than in tread compounds. Every CB grade has two major properties that determine its properties.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -663,7 +663,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>emulsion SBR [Arlanxeo]</t>
+          <t>gel permeation chromatography method [Arlanxeo]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -674,7 +674,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Polymerization is performed in an emulsion where polymer particles (and consequently, crumbs) are carried in a liquid (water) medium.</t>
+          <t>The method used to obtain the value of Mw and Mn.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -682,7 +682,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LossModulus Gdouble dash(max) [Arlanxeo]</t>
+          <t>cis content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -690,10 +690,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maximum value of loss modulus</t>
+          <t>Cis content is a quality in polymers, particularly in polyisoprene, that is crucial for determining the material's properties based on the content of cis isomer which is known for its high elasticity and tensile strength.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -701,18 +705,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>green compound [Arlanxeo]</t>
+          <t>mooney stress relaxation [Arlanxeo]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Compound that has not been vulcanized and may be heated in an oven to form of network.</t>
+          <t>Mooney stress relaxation is a quality of polymer that refers to the time-dependent process of relaxing a stress applied to a polymer. Due to their structure, polymers do not easily “forget” stress after it is applied to them.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -720,18 +724,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>carbon black [Arlanxeo]</t>
+          <t>dynamic mechanical thermal analysis [Arlanxeo]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>filler [Arlanxeo]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A filler based on structured carbon which is present in larger fractions in sidewall than in tread compounds. Every CB grade has two major properties that determine its properties.</t>
+          <t>A method in which the polymer is loaded with (pseudo-) linear, oscillating deformations in a temperature ramp, during which the values of G’ and G” at 3 critical temperatures are read and used .</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -739,18 +743,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>silica [Arlanxeo]</t>
+          <t>elastic modulus G dash 15 percent measurement1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>filler [Arlanxeo]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A filler that, together with silane, is present only in tread compounds and is used for enforcement.</t>
+          <t>Elastic modulus at 15% deformation (strain) in amplitude sweep test</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -758,7 +762,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E double dash 23 degree celcius [Arlanxeo]</t>
+          <t>S100 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -766,10 +770,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Loss modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>S100 is a quality of vulcanized compound or polymer which is the stress at deformation value 100.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -777,7 +785,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E dash 23 degree celcius [Arlanxeo]</t>
+          <t>tan Delta Peak Temperature [Arlanxeo]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -788,7 +796,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Elastic modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>temperature at maximum loss factor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -796,7 +804,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>solution SBR [Arlanxeo]</t>
+          <t>ramp [Arlanxeo]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -807,7 +815,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Polymerization is performed in a solution where polymer molecules are dissolved in a solvent (e.g. hexane).</t>
+          <t>In physical testing, it refers to a constant increase or decrease of testing parameters such as deformation frequency, deformation amplitude or temperature.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -815,18 +823,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>molecular weight distribution [Arlanxeo]</t>
+          <t>vulcanized compound [Arlanxeo]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ratio of Mw to Mn</t>
+          <t>Compound after being vulcanized. May also be called “vulcanizate”.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -834,18 +842,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>elastic torque at 90 percent [Arlanxeo]</t>
+          <t>styrene content [Arlanxeo]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>extensive quality</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Elastic torque value at 90% conversion measured in an MDR (Moving Die Rheometer) test</t>
+          <t>Styrene content is a quality that is a key factor in determining the properties of polymers derived from styrene.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -853,7 +865,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mechanical testing system [Arlanxeo]</t>
+          <t>shearing [Arlanxeo]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -864,7 +876,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Generic name for an instrument that applies amplitude sweeps to vulcanized rubber to assess the resistance of its network against large deformations.</t>
+          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid are forced to move parallel to each other.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -872,18 +884,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tread [Arlanxeo]</t>
+          <t>S50 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The outer surface of a tire that comes into direct contact with the road.</t>
+          <t>S50 is a quality of vulcanized compound or polymer which is the stress at deformation value 50.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -891,18 +907,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E dash 0 degree celcius [Arlanxeo]</t>
+          <t>raw polymer [Arlanxeo]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>polymer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Elastic modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Polymer (e.g. BR, SSBR) before being compounded.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -910,7 +926,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vinyl content [Arlanxeo]</t>
+          <t>elongation [Arlanxeo]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -918,14 +934,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vinyl content is a quality that is based on the vinyl content in polyethylene resins that are determined by the catalyst used for manufacturing the resin.</t>
+          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid deformed axially.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -933,7 +945,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>glass transition temperature [Arlanxeo]</t>
+          <t>LossModulus Gdouble dash(max) [Arlanxeo]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -941,14 +953,10 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The glass transition temperature (Tg) is a quality which is a phenomenon of amorphous polymers that is the temperature at which polymers undergo a transition from glassy to rubbery state marking a region of dramatic changes in the physical and mechanical properties.</t>
+          <t>Maximum value of loss modulus</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -956,22 +964,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ML1+4 [Arlanxeo]</t>
+          <t>elastic torque at 90 percent [Arlanxeo]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mooney viscosity [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>extensive quality</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ml1+4 is a quality which is mooney viscosity measured as the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
+          <t>Elastic torque value at 90% conversion measured in an MDR (Moving Die Rheometer) test</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -979,18 +983,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inner liner [Arlanxeo]</t>
+          <t>emulsion SBR [Arlanxeo]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The lining of the inner wall of a tire which prevents air from escaping.</t>
+          <t>Polymerization is performed in an emulsion where polymer particles (and consequently, crumbs) are carried in a liquid (water) medium.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -998,7 +1002,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E double dash 0 degree celcius [Arlanxeo]</t>
+          <t>die swelling first measurement [Arlanxeo]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1009,7 +1013,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Loss modulus measured at 0 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Die swell according to inhouse specification in K10 laboratory, first measurement</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1017,18 +1021,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mass per measurement time 1 [Arlanxeo]</t>
+          <t>hardness mean value [Arlanxeo]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>extensive quality</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mass throughput in an extruder, first measurement</t>
+          <t>Hardness mean value is a quality of Polymers which indicates the resistance to deformation. Average hardness value measured in Shore A scale.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1036,18 +1044,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>parts per hundred rubber [Arlanxeo]</t>
+          <t>mass per measurement time 2 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fraction of rubber compound formulations are not given based on %, so that the sum of all components will be 100%.</t>
+          <t>Mass throughput in an extruder, second measurement</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1055,18 +1063,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>filler [Arlanxeo]</t>
+          <t>tread [Arlanxeo]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Solid particles added to compound to generate enforcement.</t>
+          <t>The outer surface of a tire that comes into direct contact with the road.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1074,7 +1082,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tan Delta Peak Temperature [Arlanxeo]</t>
+          <t>tan d max [Arlanxeo]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1085,7 +1093,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>temperature at maximum loss factor</t>
+          <t>Maximum loss factor in an amplitude sweep test</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1093,18 +1101,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vulcanized compound [Arlanxeo]</t>
+          <t>mechanical testing system [Arlanxeo]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Compound after being vulcanized. May also be called “vulcanizate”.</t>
+          <t>Generic name for an instrument that applies amplitude sweeps to vulcanized rubber to assess the resistance of its network against large deformations.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1112,18 +1120,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>die swelling second measurement [Arlanxeo]</t>
+          <t>vulcanization [Arlanxeo]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Die swell according to inhouse specification in K10 laboratory, second measurement</t>
+          <t>The process of converting a polymer compound into an elastic network using vulcanization chemicals (e.g. sulfur) and heat (to start the reaction).</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1131,22 +1139,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rebound mean value 1 [Arlanxeo]</t>
+          <t>die swelling second measurement [Arlanxeo]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rebound mean value [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Rebound mean value  1 is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius.</t>
+          <t>Die swell according to inhouse specification in K10 laboratory, second measurement</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1154,22 +1158,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100 [Arlanxeo]</t>
+          <t>mass per measurement time 1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>extensive quality</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>S100 is a quality of vulcanized compound or polymer which is the stress at deformation value 100.</t>
+          <t>Mass throughput in an extruder, first measurement</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1177,22 +1177,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>number averaged molecular weight [Arlanxeo]</t>
+          <t>D Median [Arlanxeo]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>molecular weight [mi]</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Average molecular weight of the chains of a polymer, calculated by weighing each chain equally, regardless of size (first moment of the molecular weight).</t>
+          <t>Median value of elongation from stress-strain (tensile) measurement</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1200,18 +1196,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>styrene-butadiene rubber [Arlanxeo]</t>
+          <t>S300 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>butadiene rubber [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rubber polymer with styrene and butadiene as monomers. It is the major component of tread compounds.</t>
+          <t>S300 is a quality of vulcanized compound or polymer which is the stress at deformation value 300.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1219,22 +1219,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>weight averaged molecular weight [Arlanxeo]</t>
+          <t>mass presssure 1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>molecular weight [mi]</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Average molecular weight of the chains of a polymer, weighted by the mass of each chain (2nd moment of the molecular weight).</t>
+          <t>Pressure at die exit in an extruder, first measurement</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1242,18 +1238,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mass presssure 1 [Arlanxeo]</t>
+          <t>ML1+4 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>mooney viscosity [Arlanxeo]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pressure at die exit in an extruder, first measurement</t>
+          <t>ml1+4 is a quality which is mooney viscosity measured as the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tan d max [Arlanxeo]</t>
+          <t>E double dash 23 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1272,7 +1272,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Maximum loss factor in an amplitude sweep test</t>
+          <t>Loss modulus measured at 23 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1280,18 +1280,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D Median [Arlanxeo]</t>
+          <t>parts per hundred rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Median value of elongation from stress-strain (tensile) measurement</t>
+          <t>Fraction of rubber compound formulations are not given based on %, so that the sum of all components will be 100%.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mass pressure 2 [Arlanxeo]</t>
+          <t>molecular weight distribution [Arlanxeo]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1310,7 +1310,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pressure at die exit in an extruder, second measurement</t>
+          <t>Ratio of Mw to Mn</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1318,18 +1318,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mass per measurement time 2 [Arlanxeo]</t>
+          <t>loss factor at 7 percent [Arlanxeo]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mass throughput in an extruder, second measurement</t>
+          <t>Loss factor measured at 7% deformation (strain) measured in an amplitude sweep test</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1337,12 +1337,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cis content [Arlanxeo]</t>
+          <t>number averaged molecular weight [Arlanxeo]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>molecular weight [mi]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cis content is a quality in polymers, particularly in polyisoprene, that is crucial for determining the material's properties based on the content of cis isomer which is known for its high elasticity and tensile strength.</t>
+          <t>Average molecular weight of the chains of a polymer, calculated by weighing each chain equally, regardless of size (first moment of the molecular weight).</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1360,22 +1360,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>styrene content [Arlanxeo]</t>
+          <t>silica [Arlanxeo]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>filler [Arlanxeo]</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Styrene content is a quality that is a key factor in determining the properties of polymers derived from styrene.</t>
+          <t>A filler that, together with silane, is present only in tread compounds and is used for enforcement.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1383,7 +1379,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mooney stress relaxation [Arlanxeo]</t>
+          <t>E dash 60 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1394,7 +1390,7 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mooney stress relaxation is a quality of polymer that refers to the time-dependent process of relaxing a stress applied to a polymer. Due to their structure, polymers do not easily “forget” stress after it is applied to them.</t>
+          <t>Elastic modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1402,22 +1398,18 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>trans content [Arlanxeo]</t>
+          <t>butadiene rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>chemical substance</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Trans content is a quality which measures the content of trans isomer in polymers that affect melting points and solubility in polymers.</t>
+          <t>Rubber polymer with butadiene as its only monomer.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1425,7 +1417,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S50 [Arlanxeo]</t>
+          <t>rebound mean value [Arlanxeo]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1440,7 +1432,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>S50 is a quality of vulcanized compound or polymer which is the stress at deformation value 50.</t>
+          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius and T = 60 degree celcius for tire compounds.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1448,22 +1440,18 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rebound mean value 2 [Arlanxeo]</t>
+          <t>green compound [Arlanxeo]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>rebound mean value [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>mixture [chebi]</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 60 degree celcius.</t>
+          <t>Compound that has not been vulcanized and may be heated in an oven to form of network.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1471,22 +1459,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ML1+1 [Arlanxeo]</t>
+          <t>loss modulus [Arlanxeo]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>mooney viscosity [Arlanxeo]</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ml1+1 is the quality Mooney Viscosity which is the torque at t=1 min. after the start of the Mooney test.</t>
+          <t>The component of modulus that is related to energy loss in deformation.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1494,18 +1478,18 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gel permeation chromatography method [Arlanxeo]</t>
+          <t>silane [Arlanxeo]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The method used to obtain the value of Mw and Mn.</t>
+          <t>Silane is necessary to act as intermediary between silica and the SBR matrix, and its role is to enhance the dispersion of silica in the SBR matrix.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1513,22 +1497,18 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hardness mean value [Arlanxeo]</t>
+          <t>inner liner [Arlanxeo]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Pallavi Karanth</t>
-        </is>
-      </c>
+          <t>fiat object part</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hardness mean value is a quality of Polymers which indicates the resistance to deformation. Average hardness value measured in Shore A scale.</t>
+          <t>The lining of the inner wall of a tire which prevents air from escaping.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1536,18 +1516,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>silane [Arlanxeo]</t>
+          <t>filler [Arlanxeo]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Silane is necessary to act as intermediary between silica and the SBR matrix, and its role is to enhance the dispersion of silica in the SBR matrix.</t>
+          <t>Solid particles added to compound to generate enforcement.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1555,7 +1535,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>elastic modulus G dash 15 percent measurement1 [Arlanxeo]</t>
+          <t>mooney viscosity [Arlanxeo]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1563,10 +1543,14 @@
           <t>intensive quality</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Elastic modulus at 15% deformation (strain) in amplitude sweep test</t>
+          <t>Mooney Viscosity is a quality of raw and vulcanised polymersbased on the measurement of the torque necessary to rotate a disc in a cylindrical chamber filled with the rubber compound to be vulcanized and is reported in arbitrary Mooney units. It is the torque at t=5 min. after the start of the Mooney test for vulcanized polymers.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -1574,7 +1558,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>die swelling first measurement [Arlanxeo]</t>
+          <t>E double dash 60 degree celcius [Arlanxeo]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1585,7 +1569,7 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Die swell according to inhouse specification in K10 laboratory, first measurement</t>
+          <t>Loss modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -1593,18 +1577,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>loss modulus [Arlanxeo]</t>
+          <t>styrene-butadiene rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>butadiene rubber [Arlanxeo]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>The component of modulus that is related to energy loss in deformation.</t>
+          <t>Rubber polymer with styrene and butadiene as monomers. It is the major component of tread compounds.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -1612,18 +1596,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>elastic modulus G dash zero point five percent measurement1 [Arlanxeo]</t>
+          <t>weight averaged molecular weight [Arlanxeo]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>molecular weight [mi]</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Elastic modulus at 0.5% deformation (strain) in amplitude sweep test</t>
+          <t>Average molecular weight of the chains of a polymer, weighted by the mass of each chain (2nd moment of the molecular weight).</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -1631,18 +1619,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>shearing [Arlanxeo]</t>
+          <t>glass transition temperature [Arlanxeo]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>In physical testing, it refers to a deformation regime in which layers of fluid or solid are forced to move parallel to each other.</t>
+          <t>The glass transition temperature (Tg) is a quality which is a phenomenon of amorphous polymers that is the temperature at which polymers undergo a transition from glassy to rubbery state marking a region of dramatic changes in the physical and mechanical properties.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -1650,18 +1642,18 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ramp [Arlanxeo]</t>
+          <t>F Median [Arlanxeo]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>In physical testing, it refers to a constant increase or decrease of testing parameters such as deformation frequency, deformation amplitude or temperature.</t>
+          <t>Median value of tensile strength at break from stress-strain (tensile) measurement</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -1669,12 +1661,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S300 [Arlanxeo]</t>
+          <t>ML1+1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>mooney viscosity [Arlanxeo]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1684,7 +1676,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>S300 is a quality of vulcanized compound or polymer which is the stress at deformation value 300.</t>
+          <t>ml1+1 is the quality Mooney Viscosity which is the torque at t=1 min. after the start of the Mooney test.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1692,18 +1684,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dynamic mechanical thermal analysis [Arlanxeo]</t>
+          <t>rebound mean value 1 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>rebound mean value [Arlanxeo]</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>A method in which the polymer is loaded with (pseudo-) linear, oscillating deformations in a temperature ramp, during which the values of G’ and G” at 3 critical temperatures are read and used .</t>
+          <t>Rebound mean value  1 is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 23 degree celcius.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -1711,18 +1707,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E dash 60 degree celcius [Arlanxeo]</t>
+          <t>rebound mean value 2 [Arlanxeo]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>rebound mean value [Arlanxeo]</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pallavi Karanth</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Elastic modulus measured at 60 °C in dynamic mechanical thermal analysis (DTMA)</t>
+          <t>Rebound mean value is a quality of polymers which specifies in percentage how far the hammer comes back after the impact, measured at T = 60 degree celcius.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
